--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,68</t>
+          <t>0,06; 0,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,63</t>
+          <t>0,2; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,99</t>
+          <t>0,17; 1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,09</t>
+          <t>0,27; 1,1</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,93</t>
+          <t>0,73; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,2</t>
+          <t>0,19; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,75</t>
+          <t>0,59; 1,72</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,78</t>
+          <t>0,73; 2,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,84</t>
+          <t>0,52; 2,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,39</t>
+          <t>0,74; 2,35</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,37; 14,42</t>
+          <t>8,41; 14,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 18,09</t>
+          <t>12,95; 17,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,65; 15,29</t>
+          <t>11,76; 15,6</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,18</t>
+          <t>1,24; 2,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,64</t>
+          <t>1,82; 2,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,3</t>
+          <t>1,65; 2,26</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7597</t>
+          <t>0; 7901</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8584</t>
+          <t>0; 7321</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 16328</t>
+          <t>0; 16230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2128</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 14192</t>
+          <t>0; 19787</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7674</t>
+          <t>0; 6678</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3468</t>
+          <t>0; 3581</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>682; 7708</t>
+          <t>656; 8424</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1952; 14472</t>
+          <t>1772; 14183</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1264; 7066</t>
+          <t>1243; 8364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4517; 17437</t>
+          <t>4355; 17620</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4242; 16467</t>
+          <t>4079; 16598</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1014; 6602</t>
+          <t>1041; 6260</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6695; 19451</t>
+          <t>6592; 19045</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2607; 10204</t>
+          <t>2689; 10516</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2791; 17253</t>
+          <t>3146; 16588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7593; 23313</t>
+          <t>7194; 22931</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23676; 40776</t>
+          <t>23781; 40403</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55520; 77034</t>
+          <t>55134; 75427</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82528; 108330</t>
+          <t>83354; 110533</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>43611; 75307</t>
+          <t>42948; 74293</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67168; 97876</t>
+          <t>67461; 98508</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>119339; 164653</t>
+          <t>118415; 162345</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,75</t>
+          <t>0,06; 0,68</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,6</t>
+          <t>0,41; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,17</t>
+          <t>0,19; 1,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,1</t>
+          <t>0,39; 1,28</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,96</t>
+          <t>0,73; 2,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,18; 1,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,72</t>
+          <t>0,61; 1,78</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,86</t>
+          <t>0,69; 2,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,73</t>
+          <t>1,52; 3,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,35</t>
+          <t>1,34; 2,87</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,29</t>
+          <t>8,09; 13,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,71</t>
+          <t>12,53; 17,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,6</t>
+          <t>11,36; 14,93</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,15</t>
+          <t>1,4; 2,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,65</t>
+          <t>2,05; 2,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,26</t>
+          <t>1,8; 2,34</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7901</t>
+          <t>0; 7352</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7321</t>
+          <t>0; 7356</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 16230</t>
+          <t>0; 22625</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 19787</t>
+          <t>0; 22734</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2782</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6678</t>
+          <t>0; 6654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3581</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>656; 8424</t>
+          <t>711; 8402</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>10698</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1772; 14183</t>
+          <t>2846; 13623</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1243; 8364</t>
+          <t>1376; 7780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4355; 17620</t>
+          <t>5666; 18424</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12514</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4079; 16598</t>
+          <t>4472; 17708</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1041; 6260</t>
+          <t>1094; 6776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6592; 19045</t>
+          <t>7377; 21742</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>16895</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2689; 10516</t>
+          <t>2793; 12136</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3146; 16588</t>
+          <t>6687; 15982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7194; 22931</t>
+          <t>11359; 24260</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64584</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95758</t>
+          <t>102128</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23781; 40403</t>
+          <t>25092; 43045</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55134; 75427</t>
+          <t>58233; 80626</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83354; 110533</t>
+          <t>88049; 115676</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>42948; 74293</t>
+          <t>49532; 79977</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67461; 98508</t>
+          <t>76532; 104053</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>118415; 162345</t>
+          <t>130647; 170365</t>
         </is>
       </c>
     </row>
